--- a/docs/testing/BVA/order & payment/Testcase_BVA_Order_Payment.xlsx
+++ b/docs/testing/BVA/order & payment/Testcase_BVA_Order_Payment.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="22188" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BVA_TestCases" sheetId="1" r:id="rId1"/>
+    <sheet name="BVA_Boundary_Values" sheetId="2" r:id="rId1"/>
+    <sheet name="BVA_TestCases" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BVA_TestCases!$A$1:$L$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">BVA_TestCases!$A$1:$L$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,250 +31,525 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Test summary / Description</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="143">
+  <si>
+    <t>Biến đầu vào</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>min+</t>
+  </si>
+  <si>
+    <t>nominal</t>
+  </si>
+  <si>
+    <t>max-</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>Tag biên</t>
+  </si>
+  <si>
+    <t>Số lượng mỗi món (quantity)</t>
+  </si>
+  <si>
+    <t>B1, B2, B3, B4, B5</t>
+  </si>
+  <si>
+    <t>Điểm tích lũy sử dụng (used_points)</t>
+  </si>
+  <si>
+    <t>B6, B7, B8, B9, B10</t>
+  </si>
+  <si>
+    <t>Đơn giá món ăn (price)</t>
+  </si>
+  <si>
+    <t>1.000</t>
+  </si>
+  <si>
+    <t>2.000</t>
+  </si>
+  <si>
+    <t>150.000</t>
+  </si>
+  <si>
+    <t>99.999.000</t>
+  </si>
+  <si>
+    <t>100.000.000</t>
+  </si>
+  <si>
+    <t>B11, B12, B13, B14, B15</t>
+  </si>
+  <si>
+    <t>Test Case ID*</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Test Summary / Description*</t>
+  </si>
+  <si>
+    <t>Trường test / Điểm biên BVA (Tag)</t>
+  </si>
+  <si>
+    <t>HTTP Method</t>
+  </si>
+  <si>
+    <t>Endpoint</t>
   </si>
   <si>
     <t>Pre-condition</t>
   </si>
   <si>
-    <t>Test steps</t>
-  </si>
-  <si>
-    <t>Inputs (test data)</t>
-  </si>
-  <si>
-    <t>Expected result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Pass/Fail</t>
+    <t>Test Steps*</t>
+  </si>
+  <si>
+    <t>Inputs (Test Data / Request)*</t>
+  </si>
+  <si>
+    <t>Expected Result*</t>
+  </si>
+  <si>
+    <t>Actual Result (Kết quả thực tế)*</t>
+  </si>
+  <si>
+    <t>Pass/Fail*</t>
+  </si>
+  <si>
+    <t>TC_AUTH_001</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Đăng nhập tài khoản Admin lấy Token JWT cấp quyền cho toàn bộ suite test BVA</t>
+  </si>
+  <si>
+    <t>Dữ liệu hợp lệ chuẩn (account, password)</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/api/auth/login</t>
+  </si>
+  <si>
+    <t>Backend hoạt động tại http://localhost:3000, DB đã seed tài khoản admin/123</t>
+  </si>
+  <si>
+    <t>1. Thiết lập Method POST /api/auth/login.
+2. Gửi Body JSON account='admin', password='123'.
+3. Kiểm tra Status 200 OK và lấy token JWT.</t>
+  </si>
+  <si>
+    <t>Headers: Content-Type: application/json
+Body:
+{
+  "account": "admin",
+  "password": "123"
+}</t>
+  </si>
+  <si>
+    <t>Status: 200 OK
+Response trả về object chứa token JWT và thông tin user có role='ADMIN'.</t>
+  </si>
+  <si>
+    <t>HTTP 200 OK. Cấp token JWT thành công và lưu vào biến admin_token.</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
   <si>
     <t>TC_BVA_BASE</t>
   </si>
   <si>
-    <t>Tất cả biến ở giá trị danh định (Nominal BVA)</t>
-  </si>
-  <si>
-    <t>Tài khoản đã đăng nhập, điểm tích lũy &gt;= 500</t>
-  </si>
-  <si>
-    <t>1. Gửi request POST đến /api/orders
-2. Kiểm tra response trả về</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 50
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 7.500.000đ, discount = 500đ, final = 7.499.500đ</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>Order &amp; Payment</t>
+  </si>
+  <si>
+    <t>Tất cả biến ở giá trị danh định Nominal BVA (quantity=50, used_points=500, price=150.000đ)</t>
+  </si>
+  <si>
+    <t>B3, B8, B13 (Nominal)</t>
+  </si>
+  <si>
+    <t>/api/orders</t>
+  </si>
+  <si>
+    <t>Tài khoản admin có điểm &gt;= 500, Product 1 có giá 150.000đ và tồn kho đủ 50</t>
+  </si>
+  <si>
+    <t>1. Thiết lập Method POST /api/orders.
+2. Header Authorization: Bearer admin_token.
+3. Gửi Body JSON danh định.
+4. Kiểm tra Status 201 Created và tổng tiền.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 500,
+  "items": [{"product_id": 1, "quantity": 50}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 7.500.000đ, discount = 500đ, final = 7.499.500đ. Lưu đơn hàng và trừ tồn kho.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Tính toán chính xác giá trị danh định.</t>
   </si>
   <si>
     <t>TC_BVA_Q_01</t>
   </si>
   <si>
-    <t>Kiểm tra số lượng món biên tối thiểu (Min = 1)</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 1
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 150.000đ, discount = 500đ, final = 149.500đ</t>
+    <t>Kiểm tra số lượng món biên tối thiểu dưới Min (quantity = 1 phần)</t>
+  </si>
+  <si>
+    <t>B1 (quantity: Min = 1)</t>
+  </si>
+  <si>
+    <t>Tài khoản đã đăng nhập, điểm tích lũy &gt;= 500, Product 1 giá 150.000đ</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /api/orders với quantity = 1.
+2. Kiểm tra Response tính đúng total = 1 * 150.000đ.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 500,
+  "items": [{"product_id": 1, "quantity": 1}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 150.000đ, discount = 500đ, final = 149.500đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu biên tối thiểu số lượng.</t>
   </si>
   <si>
     <t>TC_BVA_Q_02</t>
   </si>
   <si>
-    <t>Kiểm tra số lượng món lân cận tối thiểu (Min+ = 2)</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 2
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 300.000đ, discount = 500đ, final = 299.500đ</t>
+    <t>Kiểm tra số lượng món lân cận tối thiểu Min+ (quantity = 2 phần)</t>
+  </si>
+  <si>
+    <t>B2 (quantity: Min+ = 2)</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /api/orders với quantity = 2.
+2. Kiểm tra Response tính đúng total = 2 * 150.000đ.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 500,
+  "items": [{"product_id": 1, "quantity": 2}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 300.000đ, discount = 500đ, final = 299.500đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu lân cận tối thiểu số lượng.</t>
   </si>
   <si>
     <t>TC_BVA_Q_03</t>
   </si>
   <si>
-    <t>Kiểm tra số lượng món lân cận tối đa (Max- = 98)</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 98
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 14.700.000đ, discount = 500đ, final = 14.699.500đ</t>
+    <t>Kiểm tra số lượng món lân cận tối đa Max- (quantity = 98 phần)</t>
+  </si>
+  <si>
+    <t>B4 (quantity: Max- = 98)</t>
+  </si>
+  <si>
+    <t>Tài khoản đã đăng nhập, điểm tích lũy &gt;= 500, Product 1 giá 150.000đ, stock &gt;= 98</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /api/orders với quantity = 98.
+2. Kiểm tra Response tính đúng total = 98 * 150.000đ.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 500,
+  "items": [{"product_id": 1, "quantity": 98}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 14.700.000đ, discount = 500đ, final = 14.699.500đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu lân cận tối đa số lượng.</t>
   </si>
   <si>
     <t>TC_BVA_Q_04</t>
   </si>
   <si>
-    <t>Kiểm tra số lượng món biên tối đa (Max = 99)</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 99
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 14.850.000đ, discount = 500đ, final = 14.849.500đ</t>
+    <t>Kiểm tra số lượng món biên tối đa trên Max (quantity = 99 phần)</t>
+  </si>
+  <si>
+    <t>B5 (quantity: Max = 99)</t>
+  </si>
+  <si>
+    <t>Tài khoản đã đăng nhập, điểm tích lũy &gt;= 500, Product 1 giá 150.000đ, stock &gt;= 99</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /api/orders với quantity = 99.
+2. Kiểm tra Response tính đúng total = 99 * 150.000đ.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 500,
+  "items": [{"product_id": 1, "quantity": 99}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 14.850.000đ, discount = 500đ, final = 14.849.500đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu biên tối đa số lượng 99 phần.</t>
   </si>
   <si>
     <t>TC_BVA_P_01</t>
   </si>
   <si>
-    <t>Kiểm tra điểm tích lũy biên tối thiểu (Min = 0)</t>
+    <t>Kiểm tra điểm tích lũy biên tối thiểu Min (used_points = 0 điểm)</t>
+  </si>
+  <si>
+    <t>B6 (used_points: Min = 0)</t>
   </si>
   <si>
     <t>Tài khoản đã đăng nhập</t>
   </si>
   <si>
-    <t>used_points: 0
-quantity: 50
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 7.500.000đ, discount = 0đ, final = 7.500.000đ</t>
+    <t>1. Gửi request POST /api/orders với used_points = 0.
+2. Kiểm tra chiết khấu discountAmount = 0đ.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 0,
+  "items": [{"product_id": 1, "quantity": 50}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 7.500.000đ, discount = 0đ, final = 7.500.000đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu không dùng điểm tích lũy.</t>
   </si>
   <si>
     <t>TC_BVA_P_02</t>
   </si>
   <si>
-    <t>Kiểm tra điểm tích lũy lân cận tối thiểu (Min+ = 1)</t>
+    <t>Kiểm tra điểm tích lũy lân cận tối thiểu Min+ (used_points = 1 điểm)</t>
+  </si>
+  <si>
+    <t>B7 (used_points: Min+ = 1)</t>
   </si>
   <si>
     <t>Tài khoản đã đăng nhập, điểm tích lũy &gt;= 1</t>
   </si>
   <si>
-    <t>used_points: 1
-quantity: 50
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 7.500.000đ, discount = 1đ, final = 7.499.999đ</t>
+    <t>1. Gửi request POST /api/orders với used_points = 1.
+2. Kiểm tra chiết khấu discountAmount = 1đ.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 1,
+  "items": [{"product_id": 1, "quantity": 50}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 7.500.000đ, discount = 1đ, final = 7.499.999đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu giảm trừ 1 điểm.</t>
   </si>
   <si>
     <t>TC_BVA_P_03</t>
   </si>
   <si>
-    <t>Kiểm tra điểm tích lũy lân cận tối đa (Max- = 7.499.999)</t>
+    <t>Kiểm tra điểm tích lũy lân cận tối đa Max- (used_points = 7.499.999 điểm)</t>
+  </si>
+  <si>
+    <t>B9 (used_points: Max- = 7.499.999)</t>
   </si>
   <si>
     <t>Tài khoản đã đăng nhập, điểm tích lũy &gt;= 7.499.999</t>
   </si>
   <si>
-    <t>used_points: 7499999
-quantity: 50
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 7.500.000đ, discount = 7.499.999đ, final = 1đ</t>
+    <t>1. Gửi request POST /api/orders với used_points = 7.499.999.
+2. Kiểm tra chiết khấu gần toàn bộ hóa đơn, final = 1đ.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 7499999,
+  "items": [{"product_id": 1, "quantity": 50}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 7.500.000đ, discount = 7.499.999đ, final = 1đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu chiết khấu lân cận tối đa.</t>
   </si>
   <si>
     <t>TC_BVA_P_04</t>
   </si>
   <si>
-    <t>Kiểm tra điểm tích lũy biên tối đa (Max = 7.500.000)</t>
+    <t>Kiểm tra điểm tích lũy biên tối đa Max (used_points = 7.500.000 điểm - 100% hóa đơn)</t>
+  </si>
+  <si>
+    <t>B10 (used_points: Max = 7.500.000)</t>
   </si>
   <si>
     <t>Tài khoản đã đăng nhập, điểm tích lũy &gt;= 7.500.000</t>
   </si>
   <si>
-    <t>used_points: 7500000
-quantity: 50
-price: 150000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 7.500.000đ, discount = 7.500.000đ, final = 0đ</t>
+    <t>1. Gửi request POST /api/orders với used_points = 7.500.000.
+2. Kiểm tra chiết khấu toàn bộ hóa đơn, final = 0đ.</t>
+  </si>
+  <si>
+    <t>Headers: Bearer {{admin_token}}
+Body:
+{
+  "table_id": 1,
+  "used_points": 7500000,
+  "items": [{"product_id": 1, "quantity": 50}]
+}</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 7.500.000đ, discount = 7.500.000đ, final = 0đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu chiết khấu tối đa toàn bộ hóa đơn 0đ.</t>
   </si>
   <si>
     <t>TC_BVA_S_01</t>
   </si>
   <si>
-    <t>Kiểm tra đơn giá món biên tối thiểu (Min = 1.000đ)</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 50
-price: 1000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 50.000đ, discount = 500đ, final = 49.500đ</t>
+    <t>Kiểm tra đơn giá món biên tối thiểu Min (price = 1.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>B11 (price: Min = 1.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>Món ăn có giá 1.000đ trong CSDL, tài khoản điểm &gt;= 500</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /api/orders đặt 50 món giá 1.000đ.
+2. Kiểm tra total = 50 * 1.000đ = 50.000đ.</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 50.000đ, discount = 500đ, final = 49.500đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu đơn giá biên tối thiểu 1.000đ.</t>
   </si>
   <si>
     <t>TC_BVA_S_02</t>
   </si>
   <si>
-    <t>Kiểm tra đơn giá món lân cận tối thiểu (Min+ = 2.000đ)</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 50
-price: 2000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 100.000đ, discount = 500đ, final = 99.500đ</t>
+    <t>Kiểm tra đơn giá món lân cận tối thiểu Min+ (price = 2.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>B12 (price: Min+ = 2.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>Món ăn có giá 2.000đ trong CSDL, tài khoản điểm &gt;= 500</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /api/orders đặt 50 món giá 2.000đ.
+2. Kiểm tra total = 50 * 2.000đ = 100.000đ.</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 100.000đ, discount = 500đ, final = 99.500đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu đơn giá lân cận tối thiểu 2.000đ.</t>
   </si>
   <si>
     <t>TC_BVA_S_03</t>
   </si>
   <si>
-    <t>Kiểm tra đơn giá món lân cận tối đa (Max- = 99.999.000đ)</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 50
-price: 99999000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 4.999.950.000đ, discount = 500đ, final = 4.999.949.500đ</t>
+    <t>Kiểm tra đơn giá món lân cận tối đa Max- (price = 99.999.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>B14 (price: Max- = 99.999.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>Món ăn có giá 99.999.000đ trong CSDL, tài khoản điểm &gt;= 500</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /api/orders đặt 50 món giá 99.999.000đ.
+2. Kiểm tra total = 50 * 99.999.000đ = 4.999.950.000đ.</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 4.999.950.000đ, discount = 500đ, final = 4.999.949.500đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu đơn giá lân cận tối đa.</t>
   </si>
   <si>
     <t>TC_BVA_S_04</t>
   </si>
   <si>
-    <t>Kiểm tra đơn giá món biên tối đa (Max = 100.000.000đ)</t>
-  </si>
-  <si>
-    <t>used_points: 500
-quantity: 50
-price: 100000000</t>
-  </si>
-  <si>
-    <t>HTTP 201 Created;
-total = 5.000.000.000đ, discount = 500đ, final = 4.999.999.500đ</t>
+    <t>Kiểm tra đơn giá món biên tối đa Max (price = 100.000.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>B15 (price: Max = 100.000.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>Món ăn có giá 100.000.000đ trong CSDL, tài khoản điểm &gt;= 500</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /api/orders đặt 50 món giá 100.000.000đ.
+2. Kiểm tra total = 50 * 100.000.000đ = 5.000.000.000đ.</t>
+  </si>
+  <si>
+    <t>Status: 201 Created
+total = 5.000.000.000đ, discount = 500đ, final = 4.999.999.500đ.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Đạt yêu cầu đơn giá biên tối đa 100M.</t>
   </si>
 </sst>
 </file>
@@ -286,7 +562,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,28 +572,50 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF196F3D"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF1E293B"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF334155"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF15803D"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -329,8 +627,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF0E6251"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -478,7 +778,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,44 +787,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.25"/>
-        <bgColor rgb="FF004AC6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.25"/>
-        <bgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCFCE7"/>
-        <bgColor rgb="FFDCFCE7"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EFDF"/>
+        <bgColor rgb="FFD4EFDF"/>
       </patternFill>
     </fill>
     <fill>
@@ -535,8 +811,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="FFE8F8F5"/>
+        <bgColor rgb="FFE8F8F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -726,27 +1002,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCBD5E1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -880,178 +1141,185 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1405,640 +1673,918 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="37.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="14.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="16.5555555555556" customWidth="1"/>
+    <col min="7" max="7" width="21.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="25" customHeight="1" spans="1:7">
+      <c r="A2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="17">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17">
+        <v>2</v>
+      </c>
+      <c r="D2" s="17">
+        <v>50</v>
+      </c>
+      <c r="E2" s="17">
+        <v>98</v>
+      </c>
+      <c r="F2" s="17">
+        <v>99</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="25" customHeight="1" spans="1:7">
+      <c r="A3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17">
+        <v>0</v>
+      </c>
+      <c r="C3" s="17">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17">
+        <v>500</v>
+      </c>
+      <c r="E3" s="17">
+        <v>7499999</v>
+      </c>
+      <c r="F3" s="17">
+        <v>7500000</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="25" customHeight="1" spans="1:7">
+      <c r="A4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="41.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="33.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="33.1111111111111" style="2" customWidth="1"/>
     <col min="5" max="5" width="39.7777777777778" customWidth="1"/>
     <col min="6" max="6" width="32.1111111111111" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="26.2777777777778" customWidth="1"/>
+    <col min="10" max="10" width="25.75" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
-    <col min="12" max="12" width="12" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" ht="42" customHeight="1" spans="1:12">
-      <c r="A2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>10</v>
+    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:12">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="10"/>
-    </row>
-    <row r="3" ht="42" customHeight="1" spans="1:12">
-      <c r="A3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="13"/>
-      <c r="L3" s="10"/>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:12">
-      <c r="A4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>10</v>
+        <v>33</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="10"/>
-    </row>
-    <row r="5" ht="42" customHeight="1" spans="1:12">
-      <c r="A5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="10"/>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:12">
-      <c r="A6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>10</v>
+        <v>54</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:12">
-      <c r="A7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:12">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>39</v>
+      <c r="F6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="10"/>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:12">
-      <c r="A9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="12" t="s">
+    </row>
+    <row r="9" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A9" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="C9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:12">
-      <c r="A10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="G9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A10" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A11" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="1:12">
-      <c r="A11" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="13"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="1:12">
-      <c r="A12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" ht="42" customHeight="1" spans="1:12">
-      <c r="A13" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="13"/>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" ht="42" customHeight="1" spans="1:12">
-      <c r="A14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>10</v>
+      <c r="J12" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A13" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A14" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>130</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="10"/>
-    </row>
-    <row r="15" ht="42" customHeight="1" spans="1:12">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="10"/>
+        <v>131</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A15" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:12">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="10"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="15"/>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:12">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="10"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="15"/>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:12">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="10"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:12">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="10"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:12">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="10"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:12">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="10"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:12">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="10"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="15"/>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:12">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="10"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:12">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="10"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="15"/>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:12">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="10"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="15"/>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:12">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="10"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="15"/>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:12">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="10"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="15"/>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:12">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="10"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="15"/>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:12">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="10"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="15"/>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:12">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="10"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="15"/>
     </row>
     <row r="31" ht="42" customHeight="1" spans="1:12">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="10"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="15"/>
     </row>
     <row r="32" ht="42" customHeight="1" spans="1:12">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="10"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="15"/>
     </row>
     <row r="33" ht="42" customHeight="1" spans="1:12">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="10"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="15"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L33" etc:filterBottomFollowUsedRange="0">

--- a/docs/testing/BVA/order & payment/Testcase_BVA_Order_Payment.xlsx
+++ b/docs/testing/BVA/order & payment/Testcase_BVA_Order_Payment.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="144">
   <si>
     <t>Biến đầu vào</t>
   </si>
@@ -526,7 +526,10 @@
 total = 4.999.950.000đ, discount = 500đ, final = 4.999.949.500đ.</t>
   </si>
   <si>
-    <t>HTTP 201 Created. Đạt yêu cầu đơn giá lân cận tối đa.</t>
+    <t>HTTP 400 Bad Request. Hệ thống báo lỗi "numeric field overflow" do cột tiền tệ DECIMAL(10,2) trong Database bị tràn số khi tổng tiền đạt mức 4.999.950.000đ (~5 Tỷ VNĐ).</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
   <si>
     <t>TC_BVA_S_04</t>
@@ -549,7 +552,7 @@
 total = 5.000.000.000đ, discount = 500đ, final = 4.999.999.500đ.</t>
   </si>
   <si>
-    <t>HTTP 201 Created. Đạt yêu cầu đơn giá biên tối đa 100M.</t>
+    <t>HTTP 400 Bad Request. Hệ thống báo lỗi "numeric field overflow" do cột tiền tệ DECIMAL(10,2) trong Database bị tràn số khi tổng tiền đạt mức 5.000.000.000đ (5 Tỷ VNĐ).</t>
   </si>
 </sst>
 </file>
@@ -562,7 +565,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,6 +612,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -778,7 +788,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -800,6 +810,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD4EFDF"/>
+        <bgColor rgb="FFD4EFDF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
         <bgColor rgb="FFD4EFDF"/>
       </patternFill>
     </fill>
@@ -1141,55 +1157,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1204,74 +1217,77 @@
     <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1300,16 +1316,19 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1318,7 +1337,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1706,71 +1725,71 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="25" customHeight="1" spans="1:7">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="18">
         <v>1</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="18">
         <v>2</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="18">
         <v>50</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="18">
         <v>98</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2" s="18">
         <v>99</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="25" customHeight="1" spans="1:7">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="18">
         <v>0</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="18">
         <v>1</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="18">
         <v>500</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="18">
         <v>7499999</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="18">
         <v>7500000</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="25" customHeight="1" spans="1:7">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2328,22 +2347,22 @@
       <c r="K14" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L14" s="11" t="s">
-        <v>41</v>
+      <c r="L14" s="12" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
       <c r="A15" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>34</v>
@@ -2352,239 +2371,239 @@
         <v>46</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>41</v>
+        <v>143</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:12">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="15"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="16"/>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:12">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="15"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="16"/>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:12">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="15"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="16"/>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:12">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="15"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="16"/>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:12">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="15"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="16"/>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:12">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="15"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="16"/>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:12">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="15"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="16"/>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:12">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="15"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="16"/>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:12">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="15"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="16"/>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:12">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="15"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="16"/>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:12">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="15"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="16"/>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:12">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="15"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="16"/>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:12">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="15"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="16"/>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:12">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="15"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="16"/>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:12">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="15"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="16"/>
     </row>
     <row r="31" ht="42" customHeight="1" spans="1:12">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="15"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="16"/>
     </row>
     <row r="32" ht="42" customHeight="1" spans="1:12">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="15"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="16"/>
     </row>
     <row r="33" ht="42" customHeight="1" spans="1:12">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="15"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="16"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L33" etc:filterBottomFollowUsedRange="0">
